--- a/sample-data/brightwater/trial-balance/tb_2026-06.xlsx
+++ b/sample-data/brightwater/trial-balance/tb_2026-06.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>679010</v>
+        <v>1380000</v>
       </c>
     </row>
     <row r="6">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>685800.1</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>814812</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-821602.1</v>
+        <v>-138000</v>
       </c>
     </row>
     <row r="9">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9713</v>
+        <v>3480000</v>
       </c>
     </row>
     <row r="10">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>145515</v>
+        <v>2760000</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-152305.1</v>
+        <v>-1120000</v>
       </c>
     </row>
     <row r="13">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1438556.9</v>
+        <v>9654614</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-485020</v>
+        <v>-1940000</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-552921</v>
+        <v>-560000</v>
       </c>
     </row>
     <row r="16">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-620822</v>
+        <v>-190000</v>
       </c>
     </row>
     <row r="17">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-824525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-19426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-2502714</v>
+        <v>-2690000</v>
       </c>
     </row>
     <row r="20">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-291030</v>
+        <v>-500000</v>
       </c>
     </row>
     <row r="21">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-291030</v>
+        <v>-500000</v>
       </c>
     </row>
     <row r="22">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-97040</v>
+        <v>-22300000</v>
       </c>
     </row>
     <row r="23">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-164941</v>
+        <v>-600000</v>
       </c>
     </row>
     <row r="24">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-261981</v>
+        <v>-22900000</v>
       </c>
     </row>
     <row r="25">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>776050</v>
+        <v>17400000</v>
       </c>
     </row>
     <row r="26">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>843951</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="27">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>45642.1</v>
+        <v>3550000</v>
       </c>
     </row>
     <row r="28">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>52432.2</v>
+        <v>560000</v>
       </c>
     </row>
     <row r="29">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106753</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="30">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>174654</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="31">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>514159</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="32">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2513641.3</v>
+        <v>22275000</v>
       </c>
     </row>
     <row r="33">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>691717</v>
+        <v>320000</v>
       </c>
     </row>
     <row r="35">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>698507.1</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="36">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>827519</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="37">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-834309.1</v>
+        <v>-32000</v>
       </c>
     </row>
     <row r="38">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22420</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="39">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>90321</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="40">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>158222</v>
+        <v>640000</v>
       </c>
     </row>
     <row r="41">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-165012.1</v>
+        <v>-240000</v>
       </c>
     </row>
     <row r="42">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1489384.9</v>
+        <v>2431500</v>
       </c>
     </row>
     <row r="43">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-497727</v>
+        <v>-410000</v>
       </c>
     </row>
     <row r="44">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-565628</v>
+        <v>-125000</v>
       </c>
     </row>
     <row r="45">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-633529</v>
+        <v>-48000</v>
       </c>
     </row>
     <row r="46">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-837232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-32133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-2566249</v>
+        <v>-583000</v>
       </c>
     </row>
     <row r="49">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-303737</v>
+        <v>-150000</v>
       </c>
     </row>
     <row r="50">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-303737</v>
+        <v>-150000</v>
       </c>
     </row>
     <row r="51">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-109747</v>
+        <v>-2650000</v>
       </c>
     </row>
     <row r="52">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-177648</v>
+        <v>-95000</v>
       </c>
     </row>
     <row r="53">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-287395</v>
+        <v>-2745000</v>
       </c>
     </row>
     <row r="54">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>788757</v>
+        <v>2050000</v>
       </c>
     </row>
     <row r="55">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>856658</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="56">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>65139.2</v>
+        <v>74000</v>
       </c>
     </row>
     <row r="59">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>119460</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="60">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>187361</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="61">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>526866</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="62">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2602590.3</v>
+        <v>2336349.1</v>
       </c>
     </row>
     <row r="63">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>704424</v>
+        <v>209999.89</v>
       </c>
     </row>
     <row r="65">
@@ -1445,33 +1445,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1010</v>
+        <v>1400</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>cash - payroll</t>
+          <t>prepaid expenses</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>711214.1</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>1200</v>
-      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>accounts receivable</t>
+          <t>TOTAL ASSETS</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>840226</v>
+        <v>218499.89</v>
       </c>
     </row>
     <row r="67">
@@ -1481,15 +1473,15 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1210</v>
+        <v>2000</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>allowance for doubtful accounts</t>
+          <t>accounts payable</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-847016.1</v>
+        <v>-15000</v>
       </c>
     </row>
     <row r="68">
@@ -1499,15 +1491,15 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>inventory - finished goods</t>
+          <t>accrued liabilities</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>35127</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="69">
@@ -1517,15 +1509,15 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1400</v>
+        <v>2500</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>prepaid expenses</t>
+          <t>term loan - current</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103028</v>
+        <v>-300000</v>
       </c>
     </row>
     <row r="70">
@@ -1535,79 +1527,63 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>fixed assets</t>
+          <t>term loan - long term</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>170929</v>
+        <v>-4200000</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-4540000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>brightwater holdco</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>1510</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>accumulated depreciation</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>-177719.1</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="B72" t="n">
+        <v>3000</v>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TOTAL ASSETS</t>
+          <t>common stock</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1540212.9</v>
+        <v>-1500000</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>2000</v>
-      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>accounts payable</t>
+          <t>TOTAL EQUITY</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-510434</v>
+        <v>-1500000</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>2100</v>
-      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>accrued liabilities</t>
+          <t>TOTAL REVENUE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-578335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1617,33 +1593,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2200</v>
+        <v>5900</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>deferred revenue</t>
+          <t>interest expense</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-646236</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>2500</v>
-      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>term loan - current</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-849939</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="77">
@@ -1653,119 +1621,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2600</v>
+        <v>3900</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>term loan - long term</t>
+          <t>retained earnings</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-44840</v>
+        <v>-1402962.99</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES</t>
+          <t>GRAND TOTAL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-2629784</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>common stock</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>-316444</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>TOTAL EQUITY</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>-316444</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>5900</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>interest expense</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>539573</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>539573</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>brightwater holdco</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>3900</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>retained earnings</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>-964625.3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>964625.3</v>
+        <v>1402962.99</v>
       </c>
     </row>
   </sheetData>

--- a/sample-data/brightwater/trial-balance/tb_2026-06.xlsx
+++ b/sample-data/brightwater/trial-balance/tb_2026-06.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1380000</v>
+        <v>3080687.91</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3480000</v>
+        <v>4480000</v>
       </c>
     </row>
     <row r="10">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2760000</v>
+        <v>3360000</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9654614</v>
+        <v>12955301.91</v>
       </c>
     </row>
     <row r="14">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>320000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="35">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>890000</v>
+        <v>1090000</v>
       </c>
     </row>
     <row r="39">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>640000</v>
+        <v>755000</v>
       </c>
     </row>
     <row r="41">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2431500</v>
+        <v>3046500</v>
       </c>
     </row>
     <row r="43">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-1402962.99</v>
+        <v>-5318650.9</v>
       </c>
     </row>
     <row r="78">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1402962.99</v>
+        <v>5318650.9</v>
       </c>
     </row>
   </sheetData>
